--- a/data/trans_dic/P2C_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
+          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45,44; 62,17</t>
+          <t>45,83; 61,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43,44; 58,44</t>
+          <t>43,55; 58,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37,55; 52,73</t>
+          <t>37,95; 53,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,33</t>
+          <t>1,97; 6,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>58,64; 73,67</t>
+          <t>58,65; 72,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,3; 73,92</t>
+          <t>61,14; 74,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,15; 57,4</t>
+          <t>42,74; 57,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,25; 7,08</t>
+          <t>3,19; 7,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>54,34; 65,59</t>
+          <t>54,1; 65,67</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54,8; 65,04</t>
+          <t>54,17; 64,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42,51; 53,26</t>
+          <t>42,44; 53,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,77</t>
+          <t>2,99; 5,75</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,69; 33,9</t>
+          <t>23,31; 33,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,86; 47,24</t>
+          <t>36,65; 47,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,67; 44,9</t>
+          <t>32,61; 44,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,65; 8,22</t>
+          <t>3,5; 8,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,37; 45,72</t>
+          <t>35,43; 45,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,77; 65,06</t>
+          <t>54,99; 65,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,24; 54,11</t>
+          <t>42,62; 53,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,75; 15,38</t>
+          <t>9,95; 15,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,04; 38,76</t>
+          <t>31,11; 38,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47,54; 55,42</t>
+          <t>47,79; 55,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39,88; 47,92</t>
+          <t>39,83; 48,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,34; 10,86</t>
+          <t>7,23; 10,87</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33,65; 47,4</t>
+          <t>32,43; 46,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44,91; 58,55</t>
+          <t>44,45; 58,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,96; 46,17</t>
+          <t>31,73; 45,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,49; 8,4</t>
+          <t>3,55; 8,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42,01; 54,9</t>
+          <t>41,79; 55,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,26; 65,29</t>
+          <t>52,33; 64,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,44; 49,56</t>
+          <t>36,24; 49,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 9,73</t>
+          <t>4,83; 9,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,6; 49,37</t>
+          <t>39,39; 49,08</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>51,3; 60,43</t>
+          <t>50,9; 60,42</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36,17; 46,07</t>
+          <t>36,45; 45,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,81; 8,06</t>
+          <t>4,9; 8,16</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,75; 53,95</t>
+          <t>39,52; 54,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,54; 55,33</t>
+          <t>41,27; 54,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,44; 42,0</t>
+          <t>27,09; 41,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,36; 13,47</t>
+          <t>5,35; 12,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>43,08; 55,79</t>
+          <t>43,03; 55,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,79; 68,38</t>
+          <t>56,2; 67,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,94; 55,12</t>
+          <t>42,08; 55,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,85; 13,59</t>
+          <t>5,93; 13,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>43,2; 52,26</t>
+          <t>43,21; 52,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51,18; 59,92</t>
+          <t>51,2; 60,16</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38,07; 47,24</t>
+          <t>37,12; 47,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,77; 12,17</t>
+          <t>6,52; 12,04</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,54; 38,72</t>
+          <t>21,4; 38,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,2; 47,82</t>
+          <t>30,52; 47,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50,01; 66,17</t>
+          <t>50,27; 67,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,26; 12,94</t>
+          <t>5,02; 13,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,12; 44,18</t>
+          <t>28,59; 44,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,42; 64,74</t>
+          <t>48,69; 64,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,77; 67,91</t>
+          <t>52,62; 68,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 7,42</t>
+          <t>2,41; 7,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,04; 40,04</t>
+          <t>27,52; 39,64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43,04; 54,51</t>
+          <t>42,77; 54,49</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54,01; 65,56</t>
+          <t>53,78; 65,75</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,8; 8,24</t>
+          <t>4,11; 8,68</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>35,89; 50,89</t>
+          <t>35,21; 50,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41,51; 57,06</t>
+          <t>41,87; 57,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32,71; 47,97</t>
+          <t>32,94; 47,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,03; 14,84</t>
+          <t>8,02; 15,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32,9; 47,8</t>
+          <t>33,07; 47,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50,43; 64,28</t>
+          <t>50,32; 64,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,05; 49,8</t>
+          <t>33,8; 49,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,07; 16,14</t>
+          <t>9,08; 16,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36,46; 46,95</t>
+          <t>36,86; 47,07</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>48,51; 59,13</t>
+          <t>48,8; 59,11</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>35,55; 46,21</t>
+          <t>35,7; 46,79</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,3; 14,41</t>
+          <t>9,42; 14,39</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>30,03; 40,28</t>
+          <t>30,03; 40,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>55,96; 65,39</t>
+          <t>55,9; 66,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37,03; 47,84</t>
+          <t>36,28; 47,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,1</t>
+          <t>1,79; 4,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>47,37; 57,04</t>
+          <t>47,38; 56,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,65; 68,94</t>
+          <t>59,77; 68,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,84; 55,13</t>
+          <t>44,92; 54,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,81; 58,71</t>
+          <t>3,75; 63,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>40,75; 47,98</t>
+          <t>40,68; 47,94</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59,32; 66,31</t>
+          <t>59,33; 66,0</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42,71; 49,91</t>
+          <t>42,91; 50,17</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,27; 48,15</t>
+          <t>3,27; 46,33</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>28,69; 37,77</t>
+          <t>28,77; 37,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>41,95; 51,45</t>
+          <t>42,12; 51,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47,61; 56,81</t>
+          <t>47,32; 56,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,91; 18,54</t>
+          <t>5,74; 18,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>36,96; 44,88</t>
+          <t>36,94; 45,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>57,4; 65,49</t>
+          <t>57,53; 65,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>54,66; 62,92</t>
+          <t>54,81; 63,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>24,06; 29,91</t>
+          <t>24,05; 29,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>34,47; 40,55</t>
+          <t>34,43; 40,42</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51,88; 58,05</t>
+          <t>51,46; 57,97</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52,79; 59,13</t>
+          <t>52,74; 58,94</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,92; 22,93</t>
+          <t>12,17; 23,08</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>34,72; 39,18</t>
+          <t>34,87; 39,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>47,11; 51,56</t>
+          <t>47,11; 51,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41,86; 46,42</t>
+          <t>42,06; 46,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,1; 8,84</t>
+          <t>6,04; 8,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>43,93; 47,96</t>
+          <t>44,12; 48,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>59,71; 63,48</t>
+          <t>59,51; 63,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48,92; 53,39</t>
+          <t>49,1; 53,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,42; 32,69</t>
+          <t>11,38; 32,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>40,34; 43,43</t>
+          <t>40,34; 43,48</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>54,38; 57,44</t>
+          <t>54,27; 57,27</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46,46; 49,6</t>
+          <t>46,32; 49,57</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9,46; 21,65</t>
+          <t>9,45; 20,25</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
+          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>66759; 91343</t>
+          <t>67333; 90275</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>77210; 103856</t>
+          <t>77391; 104406</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65135; 91474</t>
+          <t>65824; 92045</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6016; 19717</t>
+          <t>6141; 19706</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>97387; 122344</t>
+          <t>97402; 120851</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>125827; 154262</t>
+          <t>127593; 155158</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>86402; 114939</t>
+          <t>85592; 115192</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9409; 20492</t>
+          <t>9232; 20467</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>170077; 205280</t>
+          <t>169319; 205532</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>211763; 251305</t>
+          <t>209310; 248189</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>158876; 199052</t>
+          <t>158604; 199098</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18003; 34676</t>
+          <t>17986; 34553</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>67750; 96937</t>
+          <t>66659; 97150</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>113622; 149667</t>
+          <t>116122; 151672</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85677; 117741</t>
+          <t>85510; 117640</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18922; 42593</t>
+          <t>18146; 42187</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>125286; 161939</t>
+          <t>125518; 162344</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>196312; 233189</t>
+          <t>197082; 234348</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>136143; 174403</t>
+          <t>137368; 173767</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50213; 79222</t>
+          <t>51226; 78400</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>198734; 248165</t>
+          <t>199134; 249505</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>320991; 374199</t>
+          <t>322702; 377229</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>233091; 280123</t>
+          <t>232851; 282968</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>75878; 112214</t>
+          <t>74728; 112304</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>63981; 90137</t>
+          <t>61679; 89038</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>92150; 120150</t>
+          <t>91208; 120667</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56781; 82026</t>
+          <t>56359; 80409</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11019; 26548</t>
+          <t>11214; 26374</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>94949; 124072</t>
+          <t>94443; 124395</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>125210; 156441</t>
+          <t>125392; 155491</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77318; 105149</t>
+          <t>76880; 105770</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17426; 33981</t>
+          <t>16862; 33875</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>164797; 205444</t>
+          <t>163911; 204262</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>228196; 268789</t>
+          <t>226384; 268734</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>140996; 179594</t>
+          <t>142078; 179207</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31977; 53615</t>
+          <t>32620; 54259</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>79151; 107420</t>
+          <t>78679; 107592</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>101251; 134881</t>
+          <t>100612; 132703</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52560; 80434</t>
+          <t>51882; 78917</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16739; 42106</t>
+          <t>16717; 39915</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>105648; 136812</t>
+          <t>105515; 135127</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>166204; 200131</t>
+          <t>164483; 197335</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>107221; 140912</t>
+          <t>107591; 141101</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27830; 64646</t>
+          <t>28190; 65245</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>191945; 232210</t>
+          <t>192012; 233623</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>274543; 321419</t>
+          <t>274659; 322726</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>170237; 211260</t>
+          <t>166003; 211632</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>53361; 95946</t>
+          <t>51367; 94883</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>23286; 41850</t>
+          <t>23128; 41869</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>43806; 69365</t>
+          <t>44270; 68567</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66910; 88540</t>
+          <t>67258; 89818</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9398; 23128</t>
+          <t>8976; 24743</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>42097; 66126</t>
+          <t>42794; 66081</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>82300; 107819</t>
+          <t>81096; 107771</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>76793; 98814</t>
+          <t>76573; 99425</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6726; 19193</t>
+          <t>6234; 19971</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>72285; 103216</t>
+          <t>70949; 102189</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>134107; 169860</t>
+          <t>133288; 169802</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>150872; 183119</t>
+          <t>150219; 183652</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16639; 36054</t>
+          <t>17964; 37968</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>58268; 82622</t>
+          <t>57163; 81730</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>73036; 100395</t>
+          <t>73674; 101120</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52742; 77339</t>
+          <t>53106; 76108</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21642; 40025</t>
+          <t>21625; 40673</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>58721; 85306</t>
+          <t>59018; 85156</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>103051; 131353</t>
+          <t>102838; 132480</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>58463; 85520</t>
+          <t>58038; 84300</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23306; 41494</t>
+          <t>23351; 41366</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>124285; 160018</t>
+          <t>125627; 160423</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>184487; 224870</t>
+          <t>185589; 224811</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>118348; 153837</t>
+          <t>118866; 155783</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>48997; 75878</t>
+          <t>49635; 75788</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>105545; 141581</t>
+          <t>105573; 141429</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>222121; 259559</t>
+          <t>221890; 262116</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>126001; 162804</t>
+          <t>123452; 162455</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11676; 31821</t>
+          <t>11156; 30076</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>209798; 252638</t>
+          <t>209874; 249844</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>272369; 314767</t>
+          <t>272930; 314118</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>198851; 244515</t>
+          <t>199235; 242667</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>32393; 498583</t>
+          <t>31877; 539246</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>323748; 381183</t>
+          <t>323198; 380874</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>506290; 565987</t>
+          <t>506426; 563382</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>334777; 391165</t>
+          <t>336338; 393226</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>48244; 709581</t>
+          <t>48126; 682632</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>133714; 176059</t>
+          <t>134109; 175516</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>199617; 244823</t>
+          <t>200420; 244410</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>217488; 259485</t>
+          <t>216158; 259990</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>54915; 172151</t>
+          <t>53328; 170976</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>199092; 241764</t>
+          <t>199026; 243422</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>338646; 386343</t>
+          <t>339406; 388259</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>319137; 367409</t>
+          <t>320062; 369165</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>172686; 214676</t>
+          <t>172601; 212743</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>346324; 407419</t>
+          <t>345990; 406147</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>552931; 618750</t>
+          <t>548516; 617897</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>549349; 615329</t>
+          <t>548823; 613389</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>196328; 377602</t>
+          <t>200412; 380059</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>663183; 748468</t>
+          <t>666019; 749273</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1006826; 1101905</t>
+          <t>1006836; 1105466</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>794075; 880538</t>
+          <t>797796; 881605</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>211217; 305947</t>
+          <t>209116; 305479</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1010970; 1103813</t>
+          <t>1015276; 1109391</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1502778; 1597594</t>
+          <t>1497883; 1594913</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1142237; 1246758</t>
+          <t>1146440; 1247762</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>423866; 1213729</t>
+          <t>422326; 1190097</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1698885; 1829024</t>
+          <t>1698777; 1830993</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2530825; 2673145</t>
+          <t>2525671; 2665308</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1966355; 2099250</t>
+          <t>1960395; 2097694</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>678344; 1552438</t>
+          <t>678095; 1452481</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45,83; 61,44</t>
+          <t>44,97; 61,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43,55; 58,75</t>
+          <t>42,43; 58,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37,95; 53,06</t>
+          <t>37,73; 52,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 6,33</t>
+          <t>1,99; 5,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>58,65; 72,77</t>
+          <t>58,42; 73,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,14; 74,35</t>
+          <t>60,97; 74,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,74; 57,52</t>
+          <t>43,73; 58,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,19; 7,07</t>
+          <t>3,82; 7,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>54,1; 65,67</t>
+          <t>54,33; 65,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54,17; 64,23</t>
+          <t>54,61; 65,56</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42,44; 53,28</t>
+          <t>42,58; 53,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 5,75</t>
+          <t>3,3; 6,0</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,31; 33,97</t>
+          <t>22,68; 33,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,65; 47,87</t>
+          <t>36,17; 48,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,61; 44,86</t>
+          <t>32,45; 44,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,5; 8,14</t>
+          <t>4,54; 9,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,43; 45,83</t>
+          <t>34,89; 45,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,99; 65,39</t>
+          <t>54,73; 64,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,62; 53,91</t>
+          <t>42,64; 53,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,95; 15,22</t>
+          <t>10,3; 15,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,11; 38,97</t>
+          <t>31,1; 38,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47,79; 55,87</t>
+          <t>47,63; 55,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39,83; 48,41</t>
+          <t>39,39; 47,97</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,23; 10,87</t>
+          <t>8,17; 11,76</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32,43; 46,82</t>
+          <t>32,57; 46,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44,45; 58,81</t>
+          <t>45,09; 58,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,73; 45,26</t>
+          <t>31,96; 46,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 8,34</t>
+          <t>3,56; 8,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41,79; 55,04</t>
+          <t>42,29; 54,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,33; 64,9</t>
+          <t>52,04; 65,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,24; 49,85</t>
+          <t>36,47; 49,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,83; 9,7</t>
+          <t>4,78; 9,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,39; 49,08</t>
+          <t>39,11; 49,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50,9; 60,42</t>
+          <t>50,87; 60,28</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36,45; 45,97</t>
+          <t>36,22; 45,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,9; 8,16</t>
+          <t>4,89; 8,13</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,52; 54,04</t>
+          <t>39,33; 53,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,27; 54,44</t>
+          <t>41,61; 55,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,09; 41,21</t>
+          <t>27,43; 40,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 12,77</t>
+          <t>5,71; 13,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>43,03; 55,1</t>
+          <t>43,58; 55,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,2; 67,43</t>
+          <t>56,15; 67,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,08; 55,19</t>
+          <t>42,1; 54,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,93; 13,72</t>
+          <t>10,16; 16,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>43,21; 52,58</t>
+          <t>43,37; 52,36</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51,2; 60,16</t>
+          <t>51,68; 60,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,12; 47,33</t>
+          <t>37,5; 47,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,52; 12,04</t>
+          <t>9,16; 14,13</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,4; 38,74</t>
+          <t>20,56; 38,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,52; 47,27</t>
+          <t>30,46; 47,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50,27; 67,13</t>
+          <t>50,65; 67,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 13,84</t>
+          <t>5,61; 13,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,59; 44,14</t>
+          <t>28,32; 44,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,69; 64,71</t>
+          <t>49,96; 64,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,62; 68,33</t>
+          <t>52,81; 68,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,41; 7,72</t>
+          <t>4,35; 9,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,52; 39,64</t>
+          <t>27,99; 39,44</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42,77; 54,49</t>
+          <t>42,83; 54,62</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53,78; 65,75</t>
+          <t>54,37; 66,02</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,11; 8,68</t>
+          <t>5,65; 10,31</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>35,21; 50,34</t>
+          <t>35,72; 50,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41,87; 57,47</t>
+          <t>42,88; 58,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32,94; 47,21</t>
+          <t>32,54; 48,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,02; 15,08</t>
+          <t>8,5; 16,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,07; 47,71</t>
+          <t>33,37; 48,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50,32; 64,83</t>
+          <t>51,84; 65,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,8; 49,09</t>
+          <t>32,96; 49,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,08; 16,09</t>
+          <t>9,47; 16,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36,86; 47,07</t>
+          <t>36,78; 47,31</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>48,8; 59,11</t>
+          <t>48,83; 59,12</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>35,7; 46,79</t>
+          <t>35,51; 46,5</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,42; 14,39</t>
+          <t>9,71; 14,74</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>30,03; 40,23</t>
+          <t>29,75; 40,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>55,9; 66,03</t>
+          <t>56,13; 66,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36,28; 47,74</t>
+          <t>36,66; 48,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,82</t>
+          <t>1,95; 4,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>47,38; 56,41</t>
+          <t>46,93; 56,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,77; 68,79</t>
+          <t>59,64; 68,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,92; 54,72</t>
+          <t>45,23; 54,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,75; 63,5</t>
+          <t>3,82; 6,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>40,68; 47,94</t>
+          <t>40,54; 47,79</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59,33; 66,0</t>
+          <t>59,15; 66,27</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42,91; 50,17</t>
+          <t>42,87; 50,23</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,27; 46,33</t>
+          <t>3,31; 5,32</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>28,77; 37,66</t>
+          <t>29,03; 37,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>42,12; 51,36</t>
+          <t>42,01; 51,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47,32; 56,92</t>
+          <t>47,82; 56,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,74; 18,41</t>
+          <t>15,07; 20,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>36,94; 45,19</t>
+          <t>36,72; 45,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>57,53; 65,81</t>
+          <t>57,24; 65,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>54,81; 63,22</t>
+          <t>54,35; 63,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>24,05; 29,64</t>
+          <t>24,7; 30,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>34,43; 40,42</t>
+          <t>34,45; 40,55</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51,46; 57,97</t>
+          <t>51,68; 57,95</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52,74; 58,94</t>
+          <t>52,72; 58,89</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,17; 23,08</t>
+          <t>20,75; 24,72</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>34,87; 39,22</t>
+          <t>34,77; 39,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>47,11; 51,72</t>
+          <t>47,28; 51,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>42,06; 46,48</t>
+          <t>42,21; 46,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,04; 8,83</t>
+          <t>7,94; 9,93</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>44,12; 48,21</t>
+          <t>44,09; 48,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>59,51; 63,37</t>
+          <t>59,67; 63,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49,1; 53,44</t>
+          <t>49,18; 53,38</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,38; 32,06</t>
+          <t>11,77; 13,84</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>40,34; 43,48</t>
+          <t>40,25; 43,36</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>54,27; 57,27</t>
+          <t>54,48; 57,5</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46,32; 49,57</t>
+          <t>46,66; 49,84</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9,45; 20,25</t>
+          <t>10,22; 11,69</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11419</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13940</t>
+          <t>17597</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25360</t>
+          <t>28571</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>67333; 90275</t>
+          <t>66079; 90180</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>77391; 104406</t>
+          <t>75417; 103694</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65824; 92045</t>
+          <t>65454; 91904</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6141; 19706</t>
+          <t>6334; 18697</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>97402; 120851</t>
+          <t>97007; 121820</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>127593; 155158</t>
+          <t>127229; 155755</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>85592; 115192</t>
+          <t>87572; 117627</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9232; 20467</t>
+          <t>12059; 24396</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>169319; 205532</t>
+          <t>170053; 203487</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>209310; 248189</t>
+          <t>211003; 253317</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>158604; 199098</t>
+          <t>159126; 199297</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17986; 34553</t>
+          <t>20975; 38063</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28666</t>
+          <t>34730</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>63856</t>
+          <t>70956</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92521</t>
+          <t>105686</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66659; 97150</t>
+          <t>64850; 96542</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>116122; 151672</t>
+          <t>114579; 152991</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85510; 117640</t>
+          <t>85084; 115443</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18146; 42187</t>
+          <t>24103; 49897</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>125518; 162344</t>
+          <t>123585; 161613</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>197082; 234348</t>
+          <t>196159; 232933</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>137368; 173767</t>
+          <t>137432; 173982</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51226; 78400</t>
+          <t>56297; 87355</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>199134; 249505</t>
+          <t>199069; 246836</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>322702; 377229</t>
+          <t>321639; 374159</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>232851; 282968</t>
+          <t>230235; 280434</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>74728; 112304</t>
+          <t>88055; 126696</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17142</t>
+          <t>17988</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24151</t>
+          <t>23873</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41293</t>
+          <t>41861</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>61679; 89038</t>
+          <t>61931; 89085</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>91208; 120667</t>
+          <t>92529; 120786</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56359; 80409</t>
+          <t>56770; 81952</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11214; 26374</t>
+          <t>11235; 27228</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>94443; 124395</t>
+          <t>95584; 123612</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>125392; 155491</t>
+          <t>124686; 156051</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>76880; 105770</t>
+          <t>77366; 105252</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16862; 33875</t>
+          <t>17028; 32743</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>163911; 204262</t>
+          <t>162781; 204399</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>226384; 268734</t>
+          <t>226267; 268105</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>142078; 179207</t>
+          <t>141186; 178844</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32620; 54259</t>
+          <t>32906; 54653</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26815</t>
+          <t>34084</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>47556</t>
+          <t>55771</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>74371</t>
+          <t>89855</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>78679; 107592</t>
+          <t>78305; 106479</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>100612; 132703</t>
+          <t>101435; 135804</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51882; 78917</t>
+          <t>52533; 78388</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16717; 39915</t>
+          <t>21318; 51844</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>105515; 135127</t>
+          <t>106885; 136504</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>164483; 197335</t>
+          <t>164321; 197397</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>107591; 141101</t>
+          <t>107624; 140153</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28190; 65245</t>
+          <t>42867; 69422</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>192012; 233623</t>
+          <t>192733; 232656</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>274659; 322726</t>
+          <t>277215; 324810</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166003; 211632</t>
+          <t>167709; 211386</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>51367; 94883</t>
+          <t>72804; 112329</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14546</t>
+          <t>18246</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12362</t>
+          <t>14885</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>26908</t>
+          <t>33131</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>23128; 41869</t>
+          <t>22221; 41453</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>44270; 68567</t>
+          <t>44186; 69476</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>67258; 89818</t>
+          <t>67773; 89785</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8976; 24743</t>
+          <t>11541; 28150</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>42794; 66081</t>
+          <t>42386; 66668</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>81096; 107771</t>
+          <t>83212; 107737</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>76573; 99425</t>
+          <t>76843; 100345</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6234; 19971</t>
+          <t>9957; 21768</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>70949; 102189</t>
+          <t>72140; 101669</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>133288; 169802</t>
+          <t>133474; 170212</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>150219; 183652</t>
+          <t>151867; 184394</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>17964; 37968</t>
+          <t>24560; 44803</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30140</t>
+          <t>31384</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>31309</t>
+          <t>32559</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>61449</t>
+          <t>63943</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>57163; 81730</t>
+          <t>57993; 82073</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>73674; 101120</t>
+          <t>75450; 102498</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>53106; 76108</t>
+          <t>52468; 77922</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21625; 40673</t>
+          <t>23003; 43370</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>59018; 85156</t>
+          <t>59554; 85918</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>102838; 132480</t>
+          <t>105945; 133380</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>58038; 84300</t>
+          <t>56603; 84455</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23351; 41366</t>
+          <t>24968; 42231</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>125627; 160423</t>
+          <t>125345; 161257</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>185589; 224811</t>
+          <t>185717; 224830</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>118866; 155783</t>
+          <t>118226; 154812</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>49635; 75788</t>
+          <t>51873; 78776</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18990</t>
+          <t>23241</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>232055</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>251044</t>
+          <t>61408</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>105573; 141429</t>
+          <t>104564; 141001</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>221890; 262116</t>
+          <t>222782; 263117</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>123452; 162455</t>
+          <t>124744; 164321</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11156; 30076</t>
+          <t>14036; 34994</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>209874; 249844</t>
+          <t>207891; 249721</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>272930; 314118</t>
+          <t>272306; 313958</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>199235; 242667</t>
+          <t>200583; 241805</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>31877; 539246</t>
+          <t>29513; 50107</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>323198; 380874</t>
+          <t>322097; 379698</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>506426; 563382</t>
+          <t>504871; 565620</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>336338; 393226</t>
+          <t>335979; 393720</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>48126; 682632</t>
+          <t>49376; 79319</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>119798</t>
+          <t>142592</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>191945</t>
+          <t>226830</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>311743</t>
+          <t>369423</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>134109; 175516</t>
+          <t>135302; 175239</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>200420; 244410</t>
+          <t>199908; 245640</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>216158; 259990</t>
+          <t>218416; 258371</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>53328; 170976</t>
+          <t>120271; 166295</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>199026; 243422</t>
+          <t>197825; 245044</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>339406; 388259</t>
+          <t>337672; 385788</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>320062; 369165</t>
+          <t>317360; 369840</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>172601; 212743</t>
+          <t>205379; 249956</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>345990; 406147</t>
+          <t>346135; 407423</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>548516; 617897</t>
+          <t>550834; 617667</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>548823; 613389</t>
+          <t>548663; 612870</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>200412; 380059</t>
+          <t>338094; 402844</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>267516</t>
+          <t>313239</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>617174</t>
+          <t>480638</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>884690</t>
+          <t>793878</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>666019; 749273</t>
+          <t>664139; 750667</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1006836; 1105466</t>
+          <t>1010607; 1101968</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>797796; 881605</t>
+          <t>800754; 881590</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>209116; 305479</t>
+          <t>280385; 350896</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1015276; 1109391</t>
+          <t>1014719; 1108578</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1497883; 1594913</t>
+          <t>1501790; 1599144</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1146440; 1247762</t>
+          <t>1148280; 1246540</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>422326; 1190097</t>
+          <t>439680; 517265</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1698777; 1830993</t>
+          <t>1695103; 1826314</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2525671; 2665308</t>
+          <t>2535549; 2675987</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1960395; 2097694</t>
+          <t>1974561; 2109294</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>678095; 1452481</t>
+          <t>743311; 849666</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
